--- a/data/trans_dic/IP16A08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 34,56</t>
+          <t>4,34; 34,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 29,34</t>
+          <t>3,24; 29,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,99; 51,44</t>
+          <t>12,39; 52,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,71; 32,05</t>
+          <t>5,97; 33,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 27,22</t>
+          <t>3,05; 24,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,95</t>
+          <t>0,0; 20,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 32,32</t>
+          <t>3,9; 34,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,3</t>
+          <t>0,0; 15,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 21,46</t>
+          <t>3,93; 22,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 19,47</t>
+          <t>4,29; 19,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,75; 35,89</t>
+          <t>12,26; 37,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 18,66</t>
+          <t>4,49; 18,07</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 37,13</t>
+          <t>6,87; 36,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,49</t>
+          <t>0,0; 14,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,2</t>
+          <t>0,0; 26,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,37</t>
+          <t>0,0; 20,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,19</t>
+          <t>0,0; 27,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,05</t>
+          <t>0,0; 29,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,35</t>
+          <t>0,0; 22,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 41,74</t>
+          <t>4,78; 42,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 27,07</t>
+          <t>6,19; 26,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 13,37</t>
+          <t>1,32; 14,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,25</t>
+          <t>0,0; 16,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 24,65</t>
+          <t>5,32; 24,42</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,02</t>
+          <t>0,0; 37,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,09</t>
+          <t>0,0; 25,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,55</t>
+          <t>0,0; 32,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,81</t>
+          <t>0,0; 48,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,6; 51,35</t>
+          <t>17,42; 51,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,01</t>
+          <t>0,0; 24,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 45,38</t>
+          <t>5,73; 45,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,45</t>
+          <t>0,0; 24,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,47; 38,89</t>
+          <t>12,98; 38,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,75</t>
+          <t>0,0; 18,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 30,79</t>
+          <t>3,49; 31,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 24,16</t>
+          <t>2,83; 24,92</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 20,59</t>
+          <t>2,44; 19,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 24,72</t>
+          <t>7,94; 25,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 17,7</t>
+          <t>4,24; 18,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 12,73</t>
+          <t>0,55; 13,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 26,84</t>
+          <t>7,29; 26,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,39; 28,08</t>
+          <t>9,94; 27,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,1; 40,72</t>
+          <t>15,07; 40,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 11,41</t>
+          <t>1,81; 11,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 19,14</t>
+          <t>7,36; 19,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,92; 23,48</t>
+          <t>10,69; 22,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 24,18</t>
+          <t>10,48; 24,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,25</t>
+          <t>2,12; 9,71</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 39,6</t>
+          <t>6,85; 38,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 33,32</t>
+          <t>8,79; 35,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 35,24</t>
+          <t>7,4; 33,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 25,98</t>
+          <t>4,18; 26,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,5</t>
+          <t>0,0; 16,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 25,99</t>
+          <t>4,07; 24,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,75; 32,3</t>
+          <t>7,97; 30,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 20,63</t>
+          <t>4,79; 20,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 25,74</t>
+          <t>8,86; 25,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 18,75</t>
+          <t>3,73; 19,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 23,92</t>
+          <t>7,66; 23,84</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,58; 75,24</t>
+          <t>18,15; 75,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,66; 41,22</t>
+          <t>4,62; 41,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,76</t>
+          <t>0,0; 24,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,46; 53,68</t>
+          <t>6,61; 53,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,62</t>
+          <t>0,0; 39,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,2</t>
+          <t>6,83; 52,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,29; 44,13</t>
+          <t>5,15; 42,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,4; 55,46</t>
+          <t>19,34; 56,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,31</t>
+          <t>0,0; 22,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,12; 38,21</t>
+          <t>8,31; 36,75</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,4; 30,27</t>
+          <t>3,09; 25,99</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,96; 22,77</t>
+          <t>10,29; 21,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 17,23</t>
+          <t>7,67; 17,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,29; 20,06</t>
+          <t>9,68; 20,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,85; 13,35</t>
+          <t>4,75; 13,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,99; 21,24</t>
+          <t>11,01; 21,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,17; 17,44</t>
+          <t>8,1; 16,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,54; 20,88</t>
+          <t>9,32; 20,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,69; 14,95</t>
+          <t>6,74; 15,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,96; 19,39</t>
+          <t>12,09; 19,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,03; 15,32</t>
+          <t>9,05; 15,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,84; 18,9</t>
+          <t>10,76; 18,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,76</t>
+          <t>6,84; 12,82</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2673</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4743</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3910</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4289</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4139</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7410</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5374</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>658; 5190</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>677; 6160</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1962; 8299</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1483; 8247</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>654; 5199</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4531</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>691; 6040</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4851</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1439; 8219</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1840; 8222</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4118; 12446</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2528; 10167</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3607</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1564</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5137</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1542</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1335; 7067</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3244</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3191</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4798</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4856</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3587</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4378</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1124; 9870</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2309; 10046</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>460; 5049</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5097</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2494; 11460</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7186</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7992</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1419</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2591</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4140</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2789</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2894</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4693</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3824; 11307</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3110</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>588; 4665</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4285</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4293; 12743</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4252</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>668; 5925</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>760; 6702</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3569</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6942</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4651</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3940</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10319</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8956</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>9482</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17261</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>13607</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>6772</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>921; 7199</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3862; 12408</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1973; 8624</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>417; 9932</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2829; 10105</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5858; 15942</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5203; 14117</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1011; 6204</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>5629; 15106</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>11500; 24498</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>8490; 19504</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2799; 12833</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3449</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5447</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4801</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3418</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3427</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>6208</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>4737</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>8874</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4801</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>9626</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1292; 7217</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2517; 10103</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1969; 8965</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1208; 7758</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3912</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1117; 6791</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2869; 11112</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2046; 8577</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4966; 14373</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1951; 10289</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4971; 15465</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3596</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2225</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3292</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2288</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2742</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4513</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1358; 5645</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>602; 5432</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2946</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>749; 6063</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5504</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>668; 5182</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>788; 6528</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3640; 10693</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4632</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1895; 8379</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>850; 7152</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>17129</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>16378</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>17623</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>21396</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>18069</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>16841</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>18609</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>38525</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>34447</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>34465</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>33595</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>11293; 23990</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>10668; 23737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11894; 25725</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>8330; 23533</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>14893; 29475</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>11882; 24843</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10905; 23957</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>12078; 27877</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>29632; 48523</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>25881; 44975</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>25797; 43998</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>24270; 45463</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 34,21</t>
+          <t>4,61; 35,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 29,44</t>
+          <t>3,26; 29,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,39; 52,38</t>
+          <t>12,11; 51,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 33,18</t>
+          <t>6,44; 34,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 24,23</t>
+          <t>3,07; 27,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,61</t>
+          <t>0,0; 20,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 34,04</t>
+          <t>3,85; 31,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,45</t>
+          <t>0,0; 15,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 22,44</t>
+          <t>5,46; 23,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 19,17</t>
+          <t>4,48; 18,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,26; 37,05</t>
+          <t>12,32; 35,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 18,07</t>
+          <t>4,03; 19,76</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 36,37</t>
+          <t>7,03; 36,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,17</t>
+          <t>0,0; 13,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,6</t>
+          <t>0,0; 21,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,48</t>
+          <t>0,0; 22,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,2</t>
+          <t>0,0; 26,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,67</t>
+          <t>0,0; 30,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,97</t>
+          <t>0,0; 22,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 42,02</t>
+          <t>7,04; 40,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 26,94</t>
+          <t>6,06; 26,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 14,43</t>
+          <t>1,34; 14,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,41</t>
+          <t>0,0; 16,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 24,42</t>
+          <t>5,25; 25,41</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,26</t>
+          <t>0,0; 28,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,37</t>
+          <t>0,0; 31,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,72</t>
+          <t>0,0; 29,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,9</t>
+          <t>0,0; 47,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 51,51</t>
+          <t>16,96; 50,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,92</t>
+          <t>0,0; 25,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 45,43</t>
+          <t>6,14; 51,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,77</t>
+          <t>0,0; 27,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,98; 38,54</t>
+          <t>13,84; 38,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,12</t>
+          <t>0,0; 18,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 31,0</t>
+          <t>3,38; 30,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 24,92</t>
+          <t>2,62; 23,42</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 19,1</t>
+          <t>3,39; 19,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 25,51</t>
+          <t>7,21; 24,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 18,55</t>
+          <t>4,17; 19,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 13,0</t>
+          <t>0,74; 12,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 26,05</t>
+          <t>7,27; 28,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 27,06</t>
+          <t>10,17; 27,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,07; 40,89</t>
+          <t>14,93; 40,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 11,11</t>
+          <t>1,66; 11,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 19,75</t>
+          <t>7,27; 19,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 22,78</t>
+          <t>11,2; 23,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,48; 24,08</t>
+          <t>10,7; 24,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 9,71</t>
+          <t>1,78; 9,4</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,85; 38,28</t>
+          <t>7,1; 37,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,79; 35,27</t>
+          <t>8,54; 36,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 33,68</t>
+          <t>8,07; 34,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 26,84</t>
+          <t>4,6; 26,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,37</t>
+          <t>0,0; 18,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 24,76</t>
+          <t>4,22; 24,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,97; 30,89</t>
+          <t>8,84; 33,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 20,06</t>
+          <t>5,97; 21,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 25,63</t>
+          <t>8,87; 26,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 19,68</t>
+          <t>4,2; 19,24</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,66; 23,84</t>
+          <t>7,89; 24,35</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,15; 75,43</t>
+          <t>19,29; 75,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,62; 41,71</t>
+          <t>4,54; 38,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,11</t>
+          <t>0,0; 24,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 53,48</t>
+          <t>11,25; 53,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,9</t>
+          <t>0,0; 30,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,83; 52,99</t>
+          <t>6,82; 52,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,15; 42,67</t>
+          <t>5,21; 46,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,34; 56,81</t>
+          <t>19,12; 53,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,21</t>
+          <t>0,0; 26,38</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,31; 36,75</t>
+          <t>7,18; 36,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 25,99</t>
+          <t>3,82; 28,83</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,29; 21,86</t>
+          <t>10,65; 22,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,67; 17,06</t>
+          <t>7,69; 17,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,68; 20,95</t>
+          <t>9,54; 20,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 13,42</t>
+          <t>4,68; 13,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,01; 21,79</t>
+          <t>11,28; 21,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,1; 16,94</t>
+          <t>8,26; 17,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,32; 20,47</t>
+          <t>9,6; 20,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,55</t>
+          <t>6,7; 15,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,09; 19,8</t>
+          <t>12,26; 19,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,05; 15,73</t>
+          <t>9,23; 15,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,76; 18,34</t>
+          <t>10,8; 18,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 12,82</t>
+          <t>6,59; 13,01</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>658; 5190</t>
+          <t>699; 5340</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>677; 6160</t>
+          <t>681; 6167</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1962; 8299</t>
+          <t>1918; 8222</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1483; 8247</t>
+          <t>1600; 8464</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>654; 5199</t>
+          <t>658; 5852</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4531</t>
+          <t>0; 4582</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>691; 6040</t>
+          <t>683; 5645</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4851</t>
+          <t>0; 4919</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1439; 8219</t>
+          <t>2001; 8441</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1840; 8222</t>
+          <t>1924; 7927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4118; 12446</t>
+          <t>4138; 11935</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2528; 10167</t>
+          <t>2267; 11117</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1335; 7067</t>
+          <t>1365; 7145</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3244</t>
+          <t>0; 3171</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3191</t>
+          <t>0; 2617</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4798</t>
+          <t>0; 5266</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4856</t>
+          <t>0; 4811</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3587</t>
+          <t>0; 3732</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4378</t>
+          <t>0; 4340</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1124; 9870</t>
+          <t>1655; 9617</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2309; 10046</t>
+          <t>2260; 9697</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>460; 5049</t>
+          <t>471; 4906</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5097</t>
+          <t>0; 5145</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2494; 11460</t>
+          <t>2465; 11923</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4140</t>
+          <t>0; 3215</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2789</t>
+          <t>0; 3489</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2894</t>
+          <t>0; 2650</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4693</t>
+          <t>0; 4551</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3824; 11307</t>
+          <t>3723; 11112</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3110</t>
+          <t>0; 3139</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>588; 4665</t>
+          <t>631; 5252</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4285</t>
+          <t>0; 4793</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4293; 12743</t>
+          <t>4576; 12688</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4252</t>
+          <t>0; 4421</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>668; 5925</t>
+          <t>645; 5743</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>760; 6702</t>
+          <t>706; 6297</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>921; 7199</t>
+          <t>1277; 7239</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3862; 12408</t>
+          <t>3505; 11783</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1973; 8624</t>
+          <t>1941; 8908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>417; 9932</t>
+          <t>568; 9744</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2829; 10105</t>
+          <t>2820; 10883</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5858; 15942</t>
+          <t>5989; 16043</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5203; 14117</t>
+          <t>5154; 14050</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1011; 6204</t>
+          <t>929; 6209</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5629; 15106</t>
+          <t>5564; 14896</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11500; 24498</t>
+          <t>12044; 24874</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8490; 19504</t>
+          <t>8671; 19835</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2799; 12833</t>
+          <t>2348; 12429</t>
         </is>
       </c>
     </row>
@@ -2759,32 +2759,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1292; 7217</t>
+          <t>1338; 6999</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2517; 10103</t>
+          <t>2447; 10450</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1969; 8965</t>
+          <t>2149; 9067</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1208; 7758</t>
+          <t>1329; 7604</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3912</t>
+          <t>0; 4411</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1117; 6791</t>
+          <t>1158; 6766</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2794,27 +2794,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2869; 11112</t>
+          <t>3179; 12184</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2046; 8577</t>
+          <t>2550; 9386</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4966; 14373</t>
+          <t>4974; 14994</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1951; 10289</t>
+          <t>2195; 10060</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4971; 15465</t>
+          <t>5118; 15801</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1358; 5645</t>
+          <t>1443; 5657</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2977,52 +2977,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>602; 5432</t>
+          <t>592; 5014</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2946</t>
+          <t>0; 2994</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>749; 6063</t>
+          <t>1276; 6091</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5504</t>
+          <t>0; 4173</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>668; 5182</t>
+          <t>667; 5162</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>788; 6528</t>
+          <t>797; 7071</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3640; 10693</t>
+          <t>3599; 10143</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4632</t>
+          <t>0; 5501</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1895; 8379</t>
+          <t>1637; 8335</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>850; 7152</t>
+          <t>1052; 7934</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11293; 23990</t>
+          <t>11683; 24139</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10668; 23737</t>
+          <t>10699; 23848</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11894; 25725</t>
+          <t>11721; 24791</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8330; 23533</t>
+          <t>8213; 23848</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14893; 29475</t>
+          <t>15261; 29191</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11882; 24843</t>
+          <t>12116; 25405</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10905; 23957</t>
+          <t>11230; 24215</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12078; 27877</t>
+          <t>12012; 27133</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>29632; 48523</t>
+          <t>30049; 48606</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25881; 44975</t>
+          <t>26369; 44464</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25797; 43998</t>
+          <t>25895; 44465</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>24270; 45463</t>
+          <t>23366; 46157</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10,19%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13,86%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12,78%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>29,93%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,19%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 35,2</t>
+          <t>3,06; 27,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 29,48</t>
+          <t>0,0; 20,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 51,89</t>
+          <t>3,87; 32,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 34,06</t>
+          <t>0,0; 14,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 27,27</t>
+          <t>4,45; 34,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,85</t>
+          <t>3,31; 29,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 31,82</t>
+          <t>11,99; 51,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,66</t>
+          <t>6,02; 34,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 23,04</t>
+          <t>4,19; 21,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 18,48</t>
+          <t>3,35; 19,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,32; 35,53</t>
+          <t>11,75; 35,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 19,76</t>
+          <t>4,24; 19,59</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>18,56%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,78%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,34%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 36,77</t>
+          <t>0,0; 29,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,85</t>
+          <t>0,0; 30,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,81</t>
+          <t>0,0; 23,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,47</t>
+          <t>5,03; 43,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,94</t>
+          <t>7,48; 37,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,88</t>
+          <t>0,0; 11,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,77</t>
+          <t>0,0; 26,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 40,94</t>
+          <t>0,0; 23,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 26,01</t>
+          <t>6,0; 27,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 14,02</t>
+          <t>1,29; 13,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,57</t>
+          <t>0,0; 17,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 25,41</t>
+          <t>6,1; 26,32</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32,74%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19,75%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7,25%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,17%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,38%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16,59%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>32,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,94</t>
+          <t>18,6; 51,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,75</t>
+          <t>0,0; 29,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,95</t>
+          <t>5,66; 45,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,43</t>
+          <t>0,0; 32,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,96; 50,62</t>
+          <t>0,0; 29,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,16</t>
+          <t>0,0; 27,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 51,15</t>
+          <t>0,0; 33,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,71</t>
+          <t>0,0; 47,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,84; 38,38</t>
+          <t>13,47; 38,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,84</t>
+          <t>0,0; 19,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 30,05</t>
+          <t>3,58; 30,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 23,42</t>
+          <t>3,34; 27,31</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15,24%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17,52%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25,94%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,47%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14,27%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15,24%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 19,21</t>
+          <t>8,16; 26,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 24,22</t>
+          <t>10,39; 28,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 19,16</t>
+          <t>15,1; 40,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 12,76</t>
+          <t>1,97; 12,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 28,06</t>
+          <t>3,45; 20,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,17; 27,23</t>
+          <t>6,53; 24,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,93; 40,7</t>
+          <t>4,26; 17,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 11,12</t>
+          <t>3,63; 20,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 19,48</t>
+          <t>7,22; 19,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,2; 23,13</t>
+          <t>10,92; 23,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,7; 24,48</t>
+          <t>10,46; 24,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 9,4</t>
+          <t>3,47; 12,54</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>18,3%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>19,02%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>18,03%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,82%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 37,13</t>
+          <t>0,0; 16,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 36,48</t>
+          <t>4,23; 25,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 34,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 26,3</t>
+          <t>6,76; 28,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,46</t>
+          <t>6,84; 39,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 24,67</t>
+          <t>7,85; 33,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,37; 35,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 33,86</t>
+          <t>4,6; 27,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 21,96</t>
+          <t>4,78; 20,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,87; 26,74</t>
+          <t>8,99; 25,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 19,24</t>
+          <t>3,9; 18,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 24,35</t>
+          <t>6,99; 22,19</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29,04%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23,4%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20,22%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>48,05%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>17,08%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>23,4%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,29; 75,59</t>
+          <t>11,46; 53,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 32,62</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 52,2</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6,43; 48,11</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>19,58; 75,24</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>4,54; 38,5</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 24,5</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>11,25; 53,73</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 30,25</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,82; 52,8</t>
+          <t>4,66; 41,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,21; 46,22</t>
+          <t>0,0; 25,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,12; 53,89</t>
+          <t>21,4; 55,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,38</t>
+          <t>0,0; 20,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,18; 36,55</t>
+          <t>9,12; 38,21</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,82; 28,83</t>
+          <t>3,64; 30,23</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15,81%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12,32%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14,39%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>15,61%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>11,77%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>14,35%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8,54%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14,39%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,65; 22,0</t>
+          <t>10,99; 21,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,69; 17,14</t>
+          <t>8,17; 17,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,54; 20,18</t>
+          <t>9,54; 20,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,68; 13,6</t>
+          <t>6,91; 15,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,28; 21,58</t>
+          <t>10,96; 22,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,26; 17,32</t>
+          <t>7,45; 17,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 20,69</t>
+          <t>9,29; 20,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 15,13</t>
+          <t>7,13; 16,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,26; 19,84</t>
+          <t>11,96; 19,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,23; 15,56</t>
+          <t>9,03; 15,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,8; 18,54</t>
+          <t>10,84; 18,9</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 13,01</t>
+          <t>8,09; 14,21</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1796,37 +1796,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2673</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4743</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3910</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1466</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5295</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>699; 5340</t>
+          <t>657; 5843</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>681; 6167</t>
+          <t>0; 4604</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1918; 8222</t>
+          <t>687; 5734</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1600; 8464</t>
+          <t>0; 4135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>658; 5852</t>
+          <t>676; 5243</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4582</t>
+          <t>692; 6137</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>683; 5645</t>
+          <t>1900; 8150</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4919</t>
+          <t>1483; 8452</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2001; 8441</t>
+          <t>1536; 7860</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1924; 7927</t>
+          <t>1435; 8353</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4138; 11935</t>
+          <t>3946; 12055</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2267; 11117</t>
+          <t>2266; 10479</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4524</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3607</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>637</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>640</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1564</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1133</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6211</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1365; 7145</t>
+          <t>0; 5212</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3171</t>
+          <t>0; 3633</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2617</t>
+          <t>0; 4452</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5266</t>
+          <t>1137; 9853</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4811</t>
+          <t>1454; 7215</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3732</t>
+          <t>0; 2632</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4340</t>
+          <t>0; 3143</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1655; 9617</t>
+          <t>0; 5302</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2260; 9697</t>
+          <t>2237; 10092</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>471; 4906</t>
+          <t>452; 4677</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5145</t>
+          <t>0; 5356</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2465; 11923</t>
+          <t>2780; 12001</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7186</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>806</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1592</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7186</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2646</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3215</t>
+          <t>4082; 11272</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3489</t>
+          <t>0; 3620</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2650</t>
+          <t>581; 4659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4551</t>
+          <t>0; 4819</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3723; 11112</t>
+          <t>0; 3224</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3139</t>
+          <t>0; 2977</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>631; 5252</t>
+          <t>0; 2967</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4793</t>
+          <t>0; 4502</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4576; 12688</t>
+          <t>4454; 12856</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4421</t>
+          <t>0; 4636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>645; 5743</t>
+          <t>684; 5886</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>706; 6297</t>
+          <t>819; 6702</t>
         </is>
       </c>
     </row>
@@ -2415,37 +2415,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10319</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8956</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2629</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3569</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6942</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4651</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3940</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5913</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10319</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8956</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6640</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1277; 7239</t>
+          <t>3164; 10412</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3505; 11783</t>
+          <t>6119; 16539</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1941; 8908</t>
+          <t>5212; 14058</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>568; 9744</t>
+          <t>979; 6097</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2820; 10883</t>
+          <t>1300; 7759</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5989; 16043</t>
+          <t>3175; 12024</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5154; 14050</t>
+          <t>1981; 8228</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>929; 6209</t>
+          <t>1545; 8554</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5564; 14896</t>
+          <t>5523; 14640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12044; 24874</t>
+          <t>11746; 25248</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8671; 19835</t>
+          <t>8478; 19588</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2348; 12429</t>
+          <t>3201; 11576</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3427</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4901</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3449</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>5447</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>4801</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3418</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3427</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>8343</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1338; 6999</t>
+          <t>0; 3943</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2447; 10450</t>
+          <t>1162; 7129</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2149; 9067</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1329; 7604</t>
+          <t>2175; 9316</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4411</t>
+          <t>1290; 7466</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1158; 6766</t>
+          <t>2248; 9544</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1961; 9381</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3179; 12184</t>
+          <t>1316; 7872</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2550; 9386</t>
+          <t>2042; 8819</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4974; 14994</t>
+          <t>5043; 14435</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2195; 10060</t>
+          <t>2039; 9803</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5118; 15801</t>
+          <t>4251; 13486</t>
         </is>
       </c>
     </row>
@@ -2836,37 +2836,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,54 +2899,54 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3292</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2288</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2854</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3596</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2225</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3292</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>984</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2288</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2742</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>6888</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
           <t>4513</t>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3439</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1443; 5657</t>
+          <t>1299; 6086</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>0; 4500</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5104</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>907; 6791</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1465; 5631</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>592; 5014</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2994</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1276; 6091</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0; 4173</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>667; 5162</t>
+          <t>607; 5370</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>797; 7071</t>
+          <t>0; 3167</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3599; 10143</t>
+          <t>4027; 10438</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5501</t>
+          <t>0; 4236</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1637; 8335</t>
+          <t>2079; 8713</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1052; 7934</t>
+          <t>967; 8031</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>21396</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>18069</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>16841</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>17083</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>17129</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>16378</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>17623</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>21396</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>18069</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>16841</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>32574</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11683; 24139</t>
+          <t>14874; 28731</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10699; 23848</t>
+          <t>11983; 25587</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11721; 24791</t>
+          <t>11164; 24436</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8213; 23848</t>
+          <t>11224; 25030</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15261; 29191</t>
+          <t>12031; 24984</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12116; 25405</t>
+          <t>10364; 23981</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11230; 24215</t>
+          <t>11411; 24635</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12012; 27133</t>
+          <t>10034; 22852</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30049; 48606</t>
+          <t>29305; 47501</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26369; 44464</t>
+          <t>25803; 43779</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25895; 44465</t>
+          <t>25991; 45325</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23366; 46157</t>
+          <t>24539; 43107</t>
         </is>
       </c>
     </row>
